--- a/config/attribute_registry.xlsx
+++ b/config/attribute_registry.xlsx
@@ -8541,7 +8541,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FREE_TEXT</t>
+          <t>ENUM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10405,7 +10405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10424,6 +10424,36 @@
           <t>value_1</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>value_2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>value_3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>value_4</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value_5</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>value_6</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>value_7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10625,7 +10655,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FREE_TEXT</t>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Grey</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11458,6 +11523,806 @@
         <is>
           <t>applicable</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>attributes__fit</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>attributes__fit_type</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>attributes__neckline</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>attributes__cuff_type</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>attributes__sleeve_length</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>attributes__comfort_level</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>attributes__finish</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>topwear</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Topwear</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>topwear_mvp</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/attribute_registry.xlsx
+++ b/config/attribute_registry.xlsx
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FREE_TEXT</t>
+          <t>ENUM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10774,7 +10774,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FREE_TEXT</t>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A-Line</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11485,7 @@
         </is>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/attribute_registry.xlsx
+++ b/config/attribute_registry.xlsx
@@ -11500,7 +11500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12327,6 +12327,7946 @@
         </is>
       </c>
       <c r="E33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>attributes__fit</t>
+        </is>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>attributes__fit_type</t>
+        </is>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>attributes__waistband_type</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pockets</t>
+        </is>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>attributes__comfort_level</t>
+        </is>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bottomwear</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bottomwear_default</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>attributes__fit</t>
+        </is>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>attributes__fit_type</t>
+        </is>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>attributes__neckline</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>attributes__sleeve_length</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>attributes__cuff_type</t>
+        </is>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pieces</t>
+        </is>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ethnic_wear</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ethnic_wear_default</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>attributes__fit</t>
+        </is>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>attributes__fit_type</t>
+        </is>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>attributes__waistband_type</t>
+        </is>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>attributes__neckline</t>
+        </is>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>attributes__sleeve_length</t>
+        </is>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>attributes__padding</t>
+        </is>
+      </c>
+      <c r="E112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>attributes__comfort_level</t>
+        </is>
+      </c>
+      <c r="E113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>inner_sleepwear</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>inner_sleepwear_default</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>attributes__outer_material</t>
+        </is>
+      </c>
+      <c r="E131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>attributes__inner_material</t>
+        </is>
+      </c>
+      <c r="E132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>attributes__sole_material</t>
+        </is>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>attributes__arch_type</t>
+        </is>
+      </c>
+      <c r="E137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>attributes__heel_height</t>
+        </is>
+      </c>
+      <c r="E138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>attributes__heel_type</t>
+        </is>
+      </c>
+      <c r="E139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>attributes__toe_shape</t>
+        </is>
+      </c>
+      <c r="E140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>attributes__grip</t>
+        </is>
+      </c>
+      <c r="E141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E144" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>attributes__comfort_level</t>
+        </is>
+      </c>
+      <c r="E146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E148" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E149" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E153" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>footwear_default</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E157" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E158" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E160" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>attributes__fit</t>
+        </is>
+      </c>
+      <c r="E167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>attributes__fit_type</t>
+        </is>
+      </c>
+      <c r="E168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>attributes__elasticity</t>
+        </is>
+      </c>
+      <c r="E169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>attributes__neckline</t>
+        </is>
+      </c>
+      <c r="E173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>attributes__sleeve_length</t>
+        </is>
+      </c>
+      <c r="E174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>attributes__waistband_type</t>
+        </is>
+      </c>
+      <c r="E175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>attributes__comfort_level</t>
+        </is>
+      </c>
+      <c r="E178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E180" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E185" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E186" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E187" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>sports_activewear</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sports_activewear_default</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E190" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E191" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E192" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E193" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E194" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E196" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>attributes__outer_material</t>
+        </is>
+      </c>
+      <c r="E197" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>attributes__inner_material</t>
+        </is>
+      </c>
+      <c r="E198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E199" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E200" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>attributes__bag_type</t>
+        </is>
+      </c>
+      <c r="E202" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>attributes__cap_type</t>
+        </is>
+      </c>
+      <c r="E203" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E204" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E205" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>attributes__lock_type</t>
+        </is>
+      </c>
+      <c r="E206" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>attributes__tsa_combination_lock</t>
+        </is>
+      </c>
+      <c r="E207" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>attributes__strap_type</t>
+        </is>
+      </c>
+      <c r="E208" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>attributes__compartments</t>
+        </is>
+      </c>
+      <c r="E209" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>attributes__laptop_compartment</t>
+        </is>
+      </c>
+      <c r="E210" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pockets</t>
+        </is>
+      </c>
+      <c r="E211" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>attributes__case_size</t>
+        </is>
+      </c>
+      <c r="E212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>attributes__band_size</t>
+        </is>
+      </c>
+      <c r="E213" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>attributes__movement_type</t>
+        </is>
+      </c>
+      <c r="E214" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>attributes__display_feature</t>
+        </is>
+      </c>
+      <c r="E215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>attributes__polarization</t>
+        </is>
+      </c>
+      <c r="E216" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>attributes__lens_color</t>
+        </is>
+      </c>
+      <c r="E217" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>attributes__lens_shape</t>
+        </is>
+      </c>
+      <c r="E218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>attributes__lens_type</t>
+        </is>
+      </c>
+      <c r="E219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>attributes__frame_color</t>
+        </is>
+      </c>
+      <c r="E220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>attributes__frame_material</t>
+        </is>
+      </c>
+      <c r="E221" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>attributes__frame_shape</t>
+        </is>
+      </c>
+      <c r="E222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>attributes__frame_size</t>
+        </is>
+      </c>
+      <c r="E223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E224" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E225" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E226" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E227" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E228" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E229" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E230" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E234" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E235" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E236" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>bags_luggage</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E239" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E241" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E242" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E243" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E244" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>attributes__outer_material</t>
+        </is>
+      </c>
+      <c r="E245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>attributes__inner_material</t>
+        </is>
+      </c>
+      <c r="E246" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E247" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E248" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E249" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>attributes__bag_type</t>
+        </is>
+      </c>
+      <c r="E250" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>attributes__cap_type</t>
+        </is>
+      </c>
+      <c r="E251" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E252" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E253" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>attributes__lock_type</t>
+        </is>
+      </c>
+      <c r="E254" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>attributes__tsa_combination_lock</t>
+        </is>
+      </c>
+      <c r="E255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>attributes__strap_type</t>
+        </is>
+      </c>
+      <c r="E256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>attributes__compartments</t>
+        </is>
+      </c>
+      <c r="E257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>attributes__laptop_compartment</t>
+        </is>
+      </c>
+      <c r="E258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pockets</t>
+        </is>
+      </c>
+      <c r="E259" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>attributes__case_size</t>
+        </is>
+      </c>
+      <c r="E260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>attributes__band_size</t>
+        </is>
+      </c>
+      <c r="E261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>attributes__movement_type</t>
+        </is>
+      </c>
+      <c r="E262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>attributes__display_feature</t>
+        </is>
+      </c>
+      <c r="E263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>attributes__polarization</t>
+        </is>
+      </c>
+      <c r="E264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>attributes__lens_color</t>
+        </is>
+      </c>
+      <c r="E265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>attributes__lens_shape</t>
+        </is>
+      </c>
+      <c r="E266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>attributes__lens_type</t>
+        </is>
+      </c>
+      <c r="E267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>attributes__frame_color</t>
+        </is>
+      </c>
+      <c r="E268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>attributes__frame_material</t>
+        </is>
+      </c>
+      <c r="E269" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>attributes__frame_shape</t>
+        </is>
+      </c>
+      <c r="E270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>attributes__frame_size</t>
+        </is>
+      </c>
+      <c r="E271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E272" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E273" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E274" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E275" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E276" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E277" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E278" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E279" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E280" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E281" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E282" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E283" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E284" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E285" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>caps_headwear</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E286" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E287" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E288" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E289" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E290" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E291" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E292" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>attributes__outer_material</t>
+        </is>
+      </c>
+      <c r="E293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>attributes__inner_material</t>
+        </is>
+      </c>
+      <c r="E294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E296" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E297" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>attributes__bag_type</t>
+        </is>
+      </c>
+      <c r="E298" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>attributes__cap_type</t>
+        </is>
+      </c>
+      <c r="E299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E300" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E301" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>attributes__lock_type</t>
+        </is>
+      </c>
+      <c r="E302" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>attributes__tsa_combination_lock</t>
+        </is>
+      </c>
+      <c r="E303" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>attributes__strap_type</t>
+        </is>
+      </c>
+      <c r="E304" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>attributes__compartments</t>
+        </is>
+      </c>
+      <c r="E305" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>attributes__laptop_compartment</t>
+        </is>
+      </c>
+      <c r="E306" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pockets</t>
+        </is>
+      </c>
+      <c r="E307" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>attributes__case_size</t>
+        </is>
+      </c>
+      <c r="E308" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>attributes__band_size</t>
+        </is>
+      </c>
+      <c r="E309" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>attributes__movement_type</t>
+        </is>
+      </c>
+      <c r="E310" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>attributes__display_feature</t>
+        </is>
+      </c>
+      <c r="E311" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>attributes__polarization</t>
+        </is>
+      </c>
+      <c r="E312" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>attributes__lens_color</t>
+        </is>
+      </c>
+      <c r="E313" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>attributes__lens_shape</t>
+        </is>
+      </c>
+      <c r="E314" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>attributes__lens_type</t>
+        </is>
+      </c>
+      <c r="E315" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>attributes__frame_color</t>
+        </is>
+      </c>
+      <c r="E316" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>attributes__frame_material</t>
+        </is>
+      </c>
+      <c r="E317" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>attributes__frame_shape</t>
+        </is>
+      </c>
+      <c r="E318" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>attributes__frame_size</t>
+        </is>
+      </c>
+      <c r="E319" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E320" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E321" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E322" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E323" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E325" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E326" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E327" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E328" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E329" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E331" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E332" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>watches</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E334" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E338" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E340" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>attributes__outer_material</t>
+        </is>
+      </c>
+      <c r="E341" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>attributes__inner_material</t>
+        </is>
+      </c>
+      <c r="E342" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E343" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E345" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>attributes__bag_type</t>
+        </is>
+      </c>
+      <c r="E346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>attributes__cap_type</t>
+        </is>
+      </c>
+      <c r="E347" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>attributes__lock_type</t>
+        </is>
+      </c>
+      <c r="E350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>attributes__tsa_combination_lock</t>
+        </is>
+      </c>
+      <c r="E351" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>attributes__strap_type</t>
+        </is>
+      </c>
+      <c r="E352" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>attributes__compartments</t>
+        </is>
+      </c>
+      <c r="E353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>attributes__laptop_compartment</t>
+        </is>
+      </c>
+      <c r="E354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pockets</t>
+        </is>
+      </c>
+      <c r="E355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>attributes__case_size</t>
+        </is>
+      </c>
+      <c r="E356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>attributes__band_size</t>
+        </is>
+      </c>
+      <c r="E357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>attributes__movement_type</t>
+        </is>
+      </c>
+      <c r="E358" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>attributes__display_feature</t>
+        </is>
+      </c>
+      <c r="E359" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>attributes__polarization</t>
+        </is>
+      </c>
+      <c r="E360" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>attributes__lens_color</t>
+        </is>
+      </c>
+      <c r="E361" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>attributes__lens_shape</t>
+        </is>
+      </c>
+      <c r="E362" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>attributes__lens_type</t>
+        </is>
+      </c>
+      <c r="E363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>attributes__frame_color</t>
+        </is>
+      </c>
+      <c r="E364" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>attributes__frame_material</t>
+        </is>
+      </c>
+      <c r="E365" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>attributes__frame_shape</t>
+        </is>
+      </c>
+      <c r="E366" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>attributes__frame_size</t>
+        </is>
+      </c>
+      <c r="E367" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E368" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E369" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E370" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E371" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E372" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E373" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E374" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E375" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E376" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E377" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E378" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E379" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E380" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E381" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>eyewear</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E382" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>attributes__brand</t>
+        </is>
+      </c>
+      <c r="E383" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>attributes__product_type</t>
+        </is>
+      </c>
+      <c r="E384" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>attributes__model</t>
+        </is>
+      </c>
+      <c r="E385" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>attributes__color</t>
+        </is>
+      </c>
+      <c r="E386" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>attributes__size</t>
+        </is>
+      </c>
+      <c r="E387" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>attributes__material</t>
+        </is>
+      </c>
+      <c r="E388" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>attributes__outer_material</t>
+        </is>
+      </c>
+      <c r="E389" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>attributes__inner_material</t>
+        </is>
+      </c>
+      <c r="E390" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>attributes__fabric</t>
+        </is>
+      </c>
+      <c r="E391" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>attributes__fabric_care</t>
+        </is>
+      </c>
+      <c r="E392" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>attributes__care_instructions</t>
+        </is>
+      </c>
+      <c r="E393" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>attributes__bag_type</t>
+        </is>
+      </c>
+      <c r="E394" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>attributes__cap_type</t>
+        </is>
+      </c>
+      <c r="E395" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>attributes__closure</t>
+        </is>
+      </c>
+      <c r="E396" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>attributes__fastening_type</t>
+        </is>
+      </c>
+      <c r="E397" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>attributes__lock_type</t>
+        </is>
+      </c>
+      <c r="E398" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>attributes__tsa_combination_lock</t>
+        </is>
+      </c>
+      <c r="E399" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>attributes__strap_type</t>
+        </is>
+      </c>
+      <c r="E400" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>attributes__compartments</t>
+        </is>
+      </c>
+      <c r="E401" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>attributes__laptop_compartment</t>
+        </is>
+      </c>
+      <c r="E402" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>attributes__no_of_pockets</t>
+        </is>
+      </c>
+      <c r="E403" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>attributes__case_size</t>
+        </is>
+      </c>
+      <c r="E404" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>attributes__band_size</t>
+        </is>
+      </c>
+      <c r="E405" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>attributes__movement_type</t>
+        </is>
+      </c>
+      <c r="E406" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>attributes__display_feature</t>
+        </is>
+      </c>
+      <c r="E407" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>attributes__polarization</t>
+        </is>
+      </c>
+      <c r="E408" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>attributes__lens_color</t>
+        </is>
+      </c>
+      <c r="E409" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>attributes__lens_shape</t>
+        </is>
+      </c>
+      <c r="E410" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>attributes__lens_type</t>
+        </is>
+      </c>
+      <c r="E411" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>attributes__frame_color</t>
+        </is>
+      </c>
+      <c r="E412" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>attributes__frame_material</t>
+        </is>
+      </c>
+      <c r="E413" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>attributes__frame_shape</t>
+        </is>
+      </c>
+      <c r="E414" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>attributes__frame_size</t>
+        </is>
+      </c>
+      <c r="E415" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>attributes__pattern</t>
+        </is>
+      </c>
+      <c r="E416" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>attributes__pattern_type</t>
+        </is>
+      </c>
+      <c r="E417" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>attributes__design</t>
+        </is>
+      </c>
+      <c r="E418" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>attributes__water_resistance</t>
+        </is>
+      </c>
+      <c r="E419" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>attributes__gender</t>
+        </is>
+      </c>
+      <c r="E420" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>attributes__age_group</t>
+        </is>
+      </c>
+      <c r="E421" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>attributes__season</t>
+        </is>
+      </c>
+      <c r="E422" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>attributes__occasion</t>
+        </is>
+      </c>
+      <c r="E423" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>attributes__occasion_type</t>
+        </is>
+      </c>
+      <c r="E424" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>attributes__package_contents</t>
+        </is>
+      </c>
+      <c r="E425" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>attributes__in_the_box</t>
+        </is>
+      </c>
+      <c r="E426" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>attributes__country_of_origin</t>
+        </is>
+      </c>
+      <c r="E427" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>attributes__weight</t>
+        </is>
+      </c>
+      <c r="E428" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>attributes__product_dimensions</t>
+        </is>
+      </c>
+      <c r="E429" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>mens_accessories</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>belts_wallets_ties_other</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>attributes__other_information</t>
+        </is>
+      </c>
+      <c r="E430" t="b">
         <v>1</v>
       </c>
     </row>
